--- a/Examples/sample.xlsx
+++ b/Examples/sample.xlsx
@@ -556,7 +556,6 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>demo</t>
@@ -582,17 +581,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>案内</t>
@@ -600,16 +588,11 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>ゆにさんチは、Excelからシナリオと演出を記述するシステムです。</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+          <t>ユニさんちゃんは、Excelからシナリオと演出を記述するシステムです。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>demo</t>
@@ -635,17 +618,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>案内</t>
@@ -656,13 +628,8 @@
           <t>この記述例には、外部モデル・音声・画像を使用していません。</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>demo</t>
@@ -688,17 +655,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>案内</t>
@@ -709,10 +665,6 @@
           <t>公開用シーンを準備した後、入力とセリフ表示を確認できます。</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:W4"/>
